--- a/data/trans_camb/IP1020-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Estudios-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,9</t>
+          <t>0,8; 7,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,88</t>
+          <t>0,97; 10,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,26</t>
+          <t>0,05; 9,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 4,24</t>
+          <t>-2,36; 4,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 13,0</t>
+          <t>-0,78; 11,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,58</t>
+          <t>1,2; 6,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,24</t>
+          <t>-1,33; 2,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,1</t>
+          <t>1,33; 9,37</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,64; —</t>
+          <t>-43,67; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,91; —</t>
+          <t>-8,27; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,21; —</t>
+          <t>-1,51; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,62</t>
+          <t>-0,05; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,03</t>
+          <t>-0,42; 2,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,87</t>
+          <t>0,54; 3,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,91</t>
+          <t>-1,1; 0,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,49</t>
+          <t>-0,74; 1,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,85</t>
+          <t>0,81; 3,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,45</t>
+          <t>-0,21; 1,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,23</t>
+          <t>-0,35; 1,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,24</t>
+          <t>1,04; 3,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 528,14</t>
+          <t>-16,16; 602,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 427,01</t>
+          <t>-35,14; 411,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 774,25</t>
+          <t>19,51; 801,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,02; 203,42</t>
+          <t>-75,85; 224,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,54; 285,05</t>
+          <t>-60,36; 304,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,15; 716,3</t>
+          <t>41,47; 779,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 245,7</t>
+          <t>-20,3; 236,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 207,28</t>
+          <t>-25,28; 217,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,06; 536,58</t>
+          <t>74,96; 527,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,59</t>
+          <t>0,28; 6,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,4</t>
+          <t>-1,53; 1,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,6</t>
+          <t>0,7; 6,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,64</t>
+          <t>-0,78; 1,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,26</t>
+          <t>0,58; 5,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,23</t>
+          <t>0,5; 5,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,11</t>
+          <t>0,13; 2,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,64</t>
+          <t>0,05; 2,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,81</t>
+          <t>1,2; 4,66</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,13; —</t>
+          <t>-57,24; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,26; —</t>
+          <t>-21,88; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 1792,81</t>
+          <t>-27,65; 1485,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 1302,6</t>
+          <t>-35,67; 1349,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48,7; 2749,3</t>
+          <t>56,91; 2238,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,04</t>
+          <t>0,75; 2,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,47</t>
+          <t>-0,37; 1,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,18</t>
+          <t>1,37; 4,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,45</t>
+          <t>-0,29; 1,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,9</t>
+          <t>-0,13; 1,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,68</t>
+          <t>1,23; 3,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,84</t>
+          <t>0,46; 1,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,37</t>
+          <t>-0,01; 1,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,57</t>
+          <t>1,58; 3,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>48,72; 745,99</t>
+          <t>53,35; 727,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 324,19</t>
+          <t>-38,64; 275,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,39; 908,53</t>
+          <t>99,48; 1030,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 259,29</t>
+          <t>-28,93; 277,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 337,86</t>
+          <t>-19,17; 316,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,63; 721,88</t>
+          <t>83,74; 674,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,69; 314,76</t>
+          <t>39,51; 315,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 236,88</t>
+          <t>-2,45; 209,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>130,96; 627,13</t>
+          <t>121,95; 585,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Estudios-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,24</t>
+          <t>0,73; 6,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,45</t>
+          <t>1,02; 10,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 9,31</t>
+          <t>0,16; 10,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,29</t>
+          <t>-2,36; 4,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 11,78</t>
+          <t>-0,21; 12,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,77</t>
+          <t>1,09; 6,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,61</t>
+          <t>-1,15; 2,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,37</t>
+          <t>1,3; 9,18</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,67; —</t>
+          <t>-60,42; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,27; —</t>
+          <t>20,48; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; —</t>
+          <t>11,45; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,88</t>
+          <t>-0,03; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,14</t>
+          <t>-0,48; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,83</t>
+          <t>0,63; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,92</t>
+          <t>-1,11; 0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,39</t>
+          <t>-0,76; 1,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,77</t>
+          <t>0,83; 3,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,46</t>
+          <t>-0,18; 1,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,33</t>
+          <t>-0,28; 1,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,33</t>
+          <t>1,06; 3,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 602,32</t>
+          <t>-20,12; 520,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 411,01</t>
+          <t>-40,79; 392,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 801,09</t>
+          <t>18,79; 767,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-75,85; 224,94</t>
+          <t>-76,85; 197,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,36; 304,2</t>
+          <t>-56,32; 274,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,47; 779,88</t>
+          <t>37,05; 823,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 236,16</t>
+          <t>-17,13; 245,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 217,33</t>
+          <t>-25,73; 213,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74,96; 527,14</t>
+          <t>77,35; 513,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,15</t>
+          <t>0,19; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,4</t>
+          <t>-1,46; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,63</t>
+          <t>0,78; 6,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,84</t>
+          <t>-1,13; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,13</t>
+          <t>0,68; 5,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,25</t>
+          <t>0,38; 4,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,97</t>
+          <t>0,12; 3,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,82</t>
+          <t>-0,0; 2,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,66</t>
+          <t>1,21; 4,67</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,24; —</t>
+          <t>-52,14; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,88; —</t>
+          <t>-25,16; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 1485,47</t>
+          <t>-23,46; 1629,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 1349,05</t>
+          <t>-32,48; 1275,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56,91; 2238,4</t>
+          <t>65,12; 2097,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,97</t>
+          <t>0,63; 2,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,38</t>
+          <t>-0,4; 1,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,1</t>
+          <t>1,3; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,46</t>
+          <t>-0,28; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,73</t>
+          <t>-0,07; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,86</t>
+          <t>1,19; 3,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,87</t>
+          <t>0,46; 1,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,28</t>
+          <t>0,04; 1,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,46</t>
+          <t>1,55; 3,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,35; 727,08</t>
+          <t>36,56; 625,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 275,26</t>
+          <t>-41,22; 344,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99,48; 1030,16</t>
+          <t>100,71; 939,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 277,98</t>
+          <t>-26,86; 306,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 316,27</t>
+          <t>-10,39; 365,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,74; 674,07</t>
+          <t>74,98; 749,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,51; 315,72</t>
+          <t>32,77; 311,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 209,83</t>
+          <t>-2,03; 209,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>121,95; 585,36</t>
+          <t>124,86; 563,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,89</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>4,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,76</t>
+          <t>0,39; 10,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>-2,35; 4,24</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 14,49</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,74; 6,9</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,02; 10,13</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,16; 10,33</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 4,35</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 12,84</t>
+          <t>1,21; 10,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,41</t>
+          <t>1,12; 6,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,56</t>
+          <t>-1,15; 2,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 9,18</t>
+          <t>1,27; 10,47</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>279,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24,15%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>323,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>279,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>284,28%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>468,48%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>562,92%</t>
+          <t>654,12%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-52,64; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-60,42; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-4,91; —</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,48; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,45; —</t>
+          <t>6,65; —</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,25</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,71</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,79</t>
+          <t>-1,11; 0,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,92</t>
+          <t>-0,68; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,99</t>
+          <t>0,76; 3,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,81</t>
+          <t>-0,06; 2,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,34</t>
+          <t>-0,46; 2,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,97</t>
+          <t>0,57; 4,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,4</t>
+          <t>-0,25; 1,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,31</t>
+          <t>-0,36; 1,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,29</t>
+          <t>1,22; 3,46</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-8,58%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>237,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>131,99%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>71,95%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>210,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-8,58%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>232,55%</t>
+          <t>240,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>221,95%</t>
+          <t>239,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 520,64</t>
+          <t>-77,02; 203,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 392,18</t>
+          <t>-59,54; 285,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 767,7</t>
+          <t>28,7; 734,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,85; 197,47</t>
+          <t>-16,85; 528,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,32; 274,74</t>
+          <t>-41,8; 427,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,05; 823,72</t>
+          <t>16,36; 846,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 245,83</t>
+          <t>-22,83; 245,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 213,99</t>
+          <t>-28,12; 207,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,35; 513,54</t>
+          <t>86,25; 556,13</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,58</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,02</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,72</t>
+          <t>-0,76; 1,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,43</t>
+          <t>0,75; 5,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,72</t>
+          <t>0,66; 5,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,52</t>
+          <t>0,34; 5,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,13</t>
+          <t>-1,45; 1,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,94</t>
+          <t>0,96; 7,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,11</t>
+          <t>0,08; 3,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,75</t>
+          <t>-0,06; 2,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,67</t>
+          <t>1,33; 5,28</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>649,86%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>681,54%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>339,46%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-2,08%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>453,14%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>649,86%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>598,73%</t>
+          <t>478,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>481,36%</t>
+          <t>531,53%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,14; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,16; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-45,13; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,59; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 1629,54</t>
+          <t>-32,1; 1792,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 1275,56</t>
+          <t>-33,2; 1302,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,12; 2097,1</t>
+          <t>60,87; 2931,08</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,79</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,92</t>
+          <t>-0,37; 1,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,38</t>
+          <t>-0,12; 1,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,02</t>
+          <t>1,29; 3,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,51</t>
+          <t>0,76; 3,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,87</t>
+          <t>-0,29; 1,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,75</t>
+          <t>1,59; 4,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,93</t>
+          <t>0,43; 1,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,31</t>
+          <t>0,07; 1,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,38</t>
+          <t>1,74; 3,74</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>56,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>90,84%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>281,32%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>226,84%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>66,41%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>325,18%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>56,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>263,72%</t>
+          <t>364,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>291,42%</t>
+          <t>318,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,56; 625,38</t>
+          <t>-36,41; 259,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 344,38</t>
+          <t>-14,51; 337,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100,71; 939,21</t>
+          <t>83,38; 745,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 306,15</t>
+          <t>48,72; 745,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 365,32</t>
+          <t>-28,3; 324,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,98; 749,78</t>
+          <t>105,37; 1007,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,77; 311,96</t>
+          <t>34,69; 314,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 209,15</t>
+          <t>-2,34; 236,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>124,86; 563,23</t>
+          <t>150,13; 680,37</t>
         </is>
       </c>
     </row>
